--- a/Supplementary Information/S5 Flow Cytometry Samples.xlsx
+++ b/Supplementary Information/S5 Flow Cytometry Samples.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\rrms\Supplementary Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB17FC8-54F2-43CA-8BEE-A5207645BB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75ED3A8-9A32-4591-8128-ACFF94082DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="2963" windowWidth="21600" windowHeight="11332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1042" yWindow="1042" windowWidth="26183" windowHeight="14408" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FLOW" sheetId="1" r:id="rId1"/>
@@ -342,7 +342,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,8 +365,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -374,44 +380,30 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB0B0B0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB0B0B0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB0B0B0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0B0B0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,1378 +707,1378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I47"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="8.796875" style="6"/>
+    <col min="1" max="2" width="12" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5">
         <v>-69</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="E2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5">
         <v>44.7</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7">
         <v>267</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="E3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="7">
         <v>45.6</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5">
         <v>-41</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="5">
         <v>43.4</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="7">
         <v>338</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="7">
         <v>44.5</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="C6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
         <v>-132</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="E6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="5">
         <v>41.8</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="G6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7">
         <v>407</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="7">
         <v>43.3</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5">
         <v>-85</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="5">
         <v>42.5</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="G8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7">
         <v>118</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="7">
         <v>43.4</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="G9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="C10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5">
         <v>-145</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="5">
         <v>28.3</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="G10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7">
         <v>-338</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="E11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="7">
         <v>27.8</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="G11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="C12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="5">
         <v>-43</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="E12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="5">
         <v>43.5</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="G12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7">
         <v>336</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="5">
+      <c r="E13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="7">
         <v>44.5</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="G13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="C14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5">
         <v>-114</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="5">
         <v>47.4</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7">
         <v>-303</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="5">
+      <c r="E15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="7">
         <v>46.9</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="C16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5">
         <v>-68</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="3">
+      <c r="E16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="5">
         <v>34.200000000000003</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="G16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7">
         <v>315</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="5">
+      <c r="E17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="7">
         <v>35.299999999999997</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="G17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="C18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="5">
         <v>-17</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="E18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="5">
         <v>48.3</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="G18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7">
         <v>-357</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="5">
+      <c r="E19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="7">
         <v>47.4</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="G19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="3">
+      <c r="C20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="5">
         <v>-87</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="5">
         <v>23.6</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="G20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7">
         <v>128</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="7">
         <v>24.5</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="G21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="3">
+      <c r="C22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="5">
         <v>-87</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="E22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="5">
         <v>33.5</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="G22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7">
         <v>258</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="5">
+      <c r="E23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="7">
         <v>34.5</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="G23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="3">
+      <c r="C24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="5">
         <v>-148</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="E24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="5">
         <v>36.5</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="3" t="s">
+      <c r="G24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7">
         <v>248</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="5">
+      <c r="E25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="7">
         <v>37.6</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="G25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="3">
+      <c r="C26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="5">
         <v>-43</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="5">
         <v>27.8</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="G26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7">
         <v>-342</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="7">
         <v>26.9</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="G27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="3">
+      <c r="C28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="5">
         <v>-112</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="5">
         <v>40.799999999999997</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="3" t="s">
+      <c r="G28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="7">
         <v>141</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="7">
         <v>43.3</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="5" t="s">
+      <c r="G29" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="3">
+      <c r="C30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="5">
         <v>-116</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="3">
+      <c r="E30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="5">
         <v>31.6</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" s="3" t="s">
+      <c r="G30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="7">
         <v>196</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="5">
+      <c r="E31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="7">
         <v>32.5</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31" s="5" t="s">
+      <c r="G31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="3">
+      <c r="C32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="5">
         <v>-88</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="E32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="5">
         <v>36.200000000000003</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="G32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C33" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="7">
         <v>-253</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="5">
+      <c r="E33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="7">
         <v>35.799999999999997</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" s="5" t="s">
+      <c r="G33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="C34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="5">
         <v>-79</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="3">
+      <c r="E34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="5">
         <v>28.3</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" s="3" t="s">
+      <c r="G34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C35" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="7">
         <v>263</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="5">
+      <c r="E35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="7">
         <v>29.2</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H35" s="5" t="s">
+      <c r="G35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="3">
+      <c r="C36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="5">
         <v>-11</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="5">
         <v>45.7</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H36" s="3" t="s">
+      <c r="G36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I36" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C37" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="7">
         <v>-303</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="7">
         <v>44.9</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H37" s="5" t="s">
+      <c r="G37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="3">
+      <c r="C38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="5">
         <v>-145</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="3">
+      <c r="E38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="5">
         <v>35.1</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H38" s="3" t="s">
+      <c r="G38" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I38" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C39" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="7">
         <v>402</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="5">
+      <c r="E39" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="7">
         <v>36.6</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" s="5" t="s">
+      <c r="G39" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="3">
+      <c r="C40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="5">
         <v>-52</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="3">
+      <c r="E40" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="5">
         <v>33.4</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="G40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C41" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="7">
         <v>194</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="5">
+      <c r="E41" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="7">
         <v>34.4</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H41" s="5" t="s">
+      <c r="G41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="3">
+      <c r="C42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="5">
         <v>-22</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="E42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="5">
         <v>29.3</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H42" s="3" t="s">
+      <c r="G42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A43" s="4" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="7">
         <v>8</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="5">
+      <c r="E43" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="7">
         <v>30.2</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H43" s="5" t="s">
+      <c r="G43" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="3">
+      <c r="C44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="5">
         <v>-30</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="E44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="5">
         <v>26.6</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H44" s="3" t="s">
+      <c r="G44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A45" s="4" t="s">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C45" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="7">
         <v>-226</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="5">
+      <c r="E45" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="7">
         <v>26</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H45" s="5" t="s">
+      <c r="G45" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="I45" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="3">
+      <c r="C46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="5">
         <v>-118</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="E46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="5">
         <v>50.1</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H46" s="3" t="s">
+      <c r="G46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="5">
+      <c r="C47" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="7">
         <v>302</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="5">
+      <c r="E47" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="7">
         <v>49.6</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47" s="5" t="s">
+      <c r="G47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" s="8" t="s">
         <v>91</v>
       </c>
     </row>
